--- a/docs/reference/Loader_Base_FinZuu_v1_1.xlsx
+++ b/docs/reference/Loader_Base_FinZuu_v1_1.xlsx
@@ -1733,7 +1733,7 @@
     <t>#144#</t>
   </si>
   <si>
-    <t>^225(07\d{8}|47\d{8}|57\d{8})$</t>
+    <t>^225(07\d{8})$</t>
   </si>
   <si>
     <t>MTN Cote d'Ivoire</t>
@@ -1745,7 +1745,7 @@
     <t>*133#</t>
   </si>
   <si>
-    <t>^225(05\d{8}|45\d{8}|55\d{8})$</t>
+    <t>^225(05\d{8})$</t>
   </si>
   <si>
     <t>Moov Africa CI</t>
@@ -1757,7 +1757,7 @@
     <t>*155#</t>
   </si>
   <si>
-    <t>^225(01\d{8}|41\d{8}|51\d{8})$</t>
+    <t>^225(01\d{8})$</t>
   </si>
   <si>
     <t>Orange Burkina Faso</t>
@@ -1766,7 +1766,7 @@
     <t>Orange BF</t>
   </si>
   <si>
-    <t>^226(0[56]\d{7}|5[45]\d{7})$</t>
+    <t>^226(0[4-7]\d{6}|4[4-6]\d{6}|5[4-7]\d{6}|6[4-7]\d{6}|7[4-7]\d{6})$</t>
   </si>
   <si>
     <t>Moov Africa Burkina</t>
@@ -1778,7 +1778,7 @@
     <t>*555#</t>
   </si>
   <si>
-    <t>^226(0[12]\d{7}|5[12]\d{7})$</t>
+    <t>^226(0[1-3]\d{6}|5[0-3]\d{6}|6[0-3]\d{6}|7[0-3]\d{6})$</t>
   </si>
   <si>
     <t>Telecel Faso</t>
@@ -1790,7 +1790,7 @@
     <t>*100#</t>
   </si>
   <si>
-    <t>^226(0[78]\d{7}|5[678]\d{7})$</t>
+    <t>^226(58\d{6}|6[89]\d{6}|7[89]\d{6})$</t>
   </si>
   <si>
     <t>Orange (Sonatel)</t>
